--- a/Result/profitability/6198.xlsx
+++ b/Result/profitability/6198.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>-0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.11625</v>
+        <v>-0.10875</v>
       </c>
       <c r="N2" t="n">
-        <v>61.23249999999999</v>
+        <v>68.12125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.39</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1475</v>
+        <v>-0.125</v>
       </c>
       <c r="N3" t="n">
-        <v>66.7075</v>
+        <v>66.105</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.26</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1475</v>
+        <v>-0.14875</v>
       </c>
       <c r="N4" t="n">
-        <v>64.94875</v>
+        <v>66.60625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.82</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.36625</v>
+        <v>-0.375</v>
       </c>
       <c r="N5" t="n">
-        <v>65.60249999999999</v>
+        <v>64.785</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.36</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.41</v>
+        <v>-0.415</v>
       </c>
       <c r="N6" t="n">
-        <v>64.265</v>
+        <v>63.39875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.47</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4637499999999999</v>
+        <v>-0.46</v>
       </c>
       <c r="N7" t="n">
-        <v>62.44</v>
+        <v>61.7625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.48125</v>
+        <v>-0.47875</v>
       </c>
       <c r="N8" t="n">
-        <v>61.0225</v>
+        <v>60.15625000000001</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6198</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>67.31</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-14</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-27788.46%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-14</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.10125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>62.59375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2000000000000001</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-6.929999999999993</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0933459051724137</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-6.539999999999992</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.08855788761002026</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
